--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -275,7 +275,7 @@
   </si>
   <si>
     <t>con-2:If category is problems list item, the clinicalStatus should not be unknown {category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and code='unknown').exists().not()}
-con-3:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission. {abatement.exists() implies (clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='inactive' or code='resolved' or code='remission')).exists())}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ischemic-etiology-only-for-ischemic-stroke:Ischemic stroke etiology extension should only be present when the diagnosis code is ischemic stroke. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and code = '422504002').exists()}hemorrhagic-bleeding-reason-only-for-hemorrhagic-stroke:Hemorrhagic bleeding reason extension should only be present when the diagnosis code is hemorrhagic stroke or subarachnoid hemorrhage. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and (code = '274100004' or code = '21454007')).exists()}wakeup-stroke-true-should-have-onset:If wake-up stroke is true, onsetDateTime should be populated with the last-known-well or sleep timestamp. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/wakeup-stroke-ext').value.ofType(boolean) != true or onset.exists()}tia-should-have-evidence:If the diagnosis is transient ischemic attack, diagnostic evidence should preferably reference the observed symptoms. {code.coding.where(system = 'http://snomed.info/sct' and code = '266257000').exists().not() or evidence.exists()}mimic-diagnosis-should-not-have-stroke-specific-extensions:If the diagnosis code belongs to MimicsDiagnosisVS, stroke-specific etiology or hemorrhagic bleeding reason extensions should not be present. {code.memberOf('http://qualityregistry.org/ValueSet/mimics-diagnosis-vs').not() or (extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() and extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not())}</t>
+con-3:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission. {abatement.exists() implies (clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='inactive' or code='resolved' or code='remission')).exists())}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ischemic-etiology-only-for-ischemic-stroke:Ischemic stroke etiology extension should only be present when the diagnosis code is ischemic stroke. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and code = '422504002').exists()}hemorrhagic-bleeding-reason-only-for-hemorrhagic-stroke:Hemorrhagic bleeding reason extension should only be present when the diagnosis code is hemorrhagic stroke or subarachnoid hemorrhage. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and (code = '274100004' or code = '21454007')).exists()}wakeup-stroke-true-should-have-onset:If wake-up stroke is true, onsetDateTime should be populated with the last-known-well or sleep timestamp. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/wakeup-stroke-ext').value.ofType(boolean) != true or onset.exists()}mimic-diagnosis-should-not-have-stroke-specific-extensions:If the diagnosis code belongs to MimicsDiagnosisVS, stroke-specific etiology or hemorrhagic bleeding reason extensions should not be present. {code.memberOf('http://qualityregistry.org/ValueSet/mimics-diagnosis-vs').not() or (extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() and extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not())}</t>
   </si>
   <si>
     <t>clinical.general</t>
@@ -1100,7 +1100,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnostic evidence supporting the stroke diagnosis</t>
+    <t>Diagnostic evidence supporting the stroke diagnosis when available in the source system</t>
   </si>
   <si>
     <t>Supporting evidence / manifestations that are the basis of the Condition's verification status, such as evidence that confirmed or refuted the condition.</t>

--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -275,7 +275,7 @@
   </si>
   <si>
     <t>con-2:If category is problems list item, the clinicalStatus should not be unknown {category.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-category' and code='problem-list-item').exists() implies clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and code='unknown').exists().not()}
-con-3:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission. {abatement.exists() implies (clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='inactive' or code='resolved' or code='remission')).exists())}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ischemic-etiology-only-for-ischemic-stroke:Ischemic stroke etiology extension should only be present when the diagnosis code is ischemic stroke. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and code = '422504002').exists()}hemorrhagic-bleeding-reason-only-for-hemorrhagic-stroke:Hemorrhagic bleeding reason extension should only be present when the diagnosis code is hemorrhagic stroke or subarachnoid hemorrhage. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and (code = '274100004' or code = '21454007')).exists()}wakeup-stroke-true-should-have-onset:If wake-up stroke is true, onsetDateTime should be populated with the last-known-well or sleep timestamp. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/wakeup-stroke-ext').value.ofType(boolean) != true or onset.exists()}mimic-diagnosis-should-not-have-stroke-specific-extensions:If the diagnosis code belongs to MimicsDiagnosisVS, stroke-specific etiology or hemorrhagic bleeding reason extensions should not be present. {code.memberOf('http://qualityregistry.org/ValueSet/mimics-diagnosis-vs').not() or (extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() and extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not())}</t>
+con-3:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission. {abatement.exists() implies (clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='inactive' or code='resolved' or code='remission')).exists())}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().ofType(canonical) | %resource.descendants().ofType(uri) | %resource.descendants().ofType(url))) or descendants().where(reference = '#').exists() or descendants().where(ofType(canonical) = '#').exists() or descendants().where(ofType(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}ischemic-etiology-only-for-ischemic-stroke:Ischemic stroke etiology extension should only be present when the diagnosis code is ischemic stroke. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and code = '422504002').exists()}hemorrhagic-bleeding-reason-only-for-hemorrhagic-stroke:Hemorrhagic bleeding reason extension should only be present when the diagnosis code is hemorrhagic stroke or subarachnoid hemorrhage. {extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not() or code.coding.where(system = 'http://snomed.info/sct' and (code = '274100004' or code = '21454007')).exists()}mimic-diagnosis-should-not-have-stroke-specific-extensions:If the diagnosis code belongs to MimicsDiagnosisVS, stroke-specific etiology or hemorrhagic bleeding reason extensions should not be present. {code.memberOf('http://qualityregistry.org/ValueSet/mimics-diagnosis-vs').not() or (extension.where(url = 'http://qualityregistry.org/StructureDefinition/ischemic-stroke-etiology-ext').exists().not() and extension.where(url = 'http://qualityregistry.org/StructureDefinition/hemorrhagic-stroke-bleeding-reason-ext').exists().not())}</t>
   </si>
   <si>
     <t>clinical.general</t>
@@ -844,7 +844,7 @@
 </t>
   </si>
   <si>
-    <t>Stroke onset or last-known-well date/time</t>
+    <t>Stroke onset or last-known-well date/time when available in the source system</t>
   </si>
   <si>
     <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>

--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
+++ b/StructureDefinition-stroke-diagnosis-condition-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
